--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>250.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>150</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>140</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>150</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>140</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>140</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>125</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>125</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>125</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>110</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>110</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>125</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>110</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>110</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>110</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>110</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>110</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45910.06753645169</v>
+        <v>45910.06753644676</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – HC KosiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12/09 16:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+128%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45910.12255452824</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>12/09 16:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,52 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45910.12255452824</v>
+        <v>45910.12255452546</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Brynas IF </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brynas IF – Vaxjo LakersSHL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+62,2%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45910.14557402749</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>100</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,232 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45910.14557402749</v>
+        <v>45910.14557402777</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – StraubingDEL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45910.18378280969</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bolzano – RB SalzbourgICE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45910.18378280969</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – Ta</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lukko – Tappara TampereFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10/09 15:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+99,3%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45910.18378280969</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Djurgaarde</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Djurgaardens IF – Skelleftea AIKSHL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+77,8%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45910.18378280969</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Brynäs IF </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brynäs IF – Växjö Lakers HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+73,9%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45910.18378280969</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -1666,10 +1666,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>140</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45910.18378280969</v>
+        <v>45910.1837828125</v>
       </c>
     </row>
     <row r="30">
@@ -1711,10 +1709,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>125</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45910.18378280969</v>
+        <v>45910.1837828125</v>
       </c>
     </row>
     <row r="31">
@@ -1756,10 +1752,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>140</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1772,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45910.18378280969</v>
+        <v>45910.1837828125</v>
       </c>
     </row>
     <row r="32">
@@ -1801,10 +1795,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>110</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1817,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45910.18378280969</v>
+        <v>45910.1837828125</v>
       </c>
     </row>
     <row r="33">
@@ -1846,10 +1838,8 @@
           <t>13/09 13:15</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>110</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1862,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45910.18378280969</v>
+        <v>45910.1837828125</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1855,6 +1855,186 @@
         <v>45910.1837828125</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Twk Inn</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HC Twk Innsbruck Die Haie – Pustertal WolfeICE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+213%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45910.27212338518</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Löwen Fran</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Löwen Frankfurt – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45910.27212338518</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Trencin – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trencin – Spisska Nova VesSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+88,1%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45910.27212338518</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Pardubice </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pardubice – Mountfield HKRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/09 16:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+61,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45910.27212338518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>200</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45910.27212338518</v>
+        <v>45910.27212337963</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>150</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45910.27212338518</v>
+        <v>45910.27212337963</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>125</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45910.27212338518</v>
+        <v>45910.27212337963</v>
       </c>
     </row>
     <row r="37">
@@ -2016,23 +2010,156 @@
           <t>10/09 16:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>110</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+61,3%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45910.27212337963</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | JYP Jyvask</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>JYP Jyvaskyla – Ilves TampereLiiga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/09 15:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>110.00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>+61,3%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>45910.27212338518</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+69,4%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45910.3057236381</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Farjestads</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Farjestads BK – Rogle BKSHL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13/09 16:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+62,2%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45910.3057236381</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Leksands I</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Leksands IF – Timrå IKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13/09 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+58,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45910.3057236381</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>10/09 15:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>110</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45910.3057236381</v>
+        <v>45910.30572363426</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>100</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45910.3057236381</v>
+        <v>45910.30572363426</v>
       </c>
     </row>
     <row r="40">
@@ -2143,10 +2139,8 @@
           <t>13/09 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2159,7 +2153,322 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45910.3057236381</v>
+        <v>45910.30572363426</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lugano – Z</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lugano – ZugSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Bern – Gen</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bern – Genève-ServetteSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+98,8%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ajoie – ZS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ajoie – ZSC LionsSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+96,1%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | J.Tjen – M</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>J.Tjen – M.OkalovaWTA - Sao Paulo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10/09 18:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+89,7%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lausanne – Fribourg GotteronSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+86,3%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kloten Fly</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kloten Flyers – Rapperswil Jona LakersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+83,6%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45910.35333440678</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Langnau Ti</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Langnau Tigers – Ambri PiottaSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+80,3%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45910.35333440678</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -2182,10 +2182,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>140</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>125</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>125</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>10/09 18:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="45">
@@ -2362,10 +2354,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>110</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2378,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="46">
@@ -2407,10 +2397,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>110</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2423,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
     <row r="47">
@@ -2452,10 +2440,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>110</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2468,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45910.35333440678</v>
+        <v>45910.35333440972</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,51 @@
         <v>45910.35333440972</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Lugano </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HC Lugano – EV ZugNational League A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45910.43163164709</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -2483,10 +2483,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>125</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45910.43163164709</v>
+        <v>45910.43163164352</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,51 @@
         <v>45910.43163164352</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>12/09 17:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45910.52916971676</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,23 +2526,156 @@
           <t>12/09 17:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>140</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+114%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45910.52916972222</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – Dukla MichalovceExtraliga</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>+114%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>45910.52916971676</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45910.56151269941</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Vienne CapitalsAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+73,2%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45910.56151269941</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SCL Tigers</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SCL Tigers – HC Ambri PiottaNational League A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+70,9%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45910.56151269941</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>140</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45910.56151269941</v>
+        <v>45910.56151269676</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>110</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45910.56151269941</v>
+        <v>45910.56151269676</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>100</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,97 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45910.56151269941</v>
+        <v>45910.56151269676</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−1.5) | Ana Candio</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ana Candiotto – Panna UdvardyWTA 250 Sao Paulo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11/09 18:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+370%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45910.59706017345</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | MSHK Zilin</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MSHK Zilina – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+205%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45910.59706017345</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>11/09 18:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>200</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45910.59706017345</v>
+        <v>45910.59706017361</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,52 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45910.59706017345</v>
+        <v>45910.59706017361</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SaiPa – Ko</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SaiPa – KooKooLiiga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+82,1%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45910.64014810004</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>125</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45910.64014810004</v>
+        <v>45910.64014810185</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SC Bern – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+84,3%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45910.68522839653</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>110</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,52 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45910.68522839653</v>
+        <v>45910.6852283912</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Black Wing</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Black Wings Linz – Pioneers VorarlbergICE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>12/09 17:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+177%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45910.72069534806</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>12/09 17:15</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>175</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,97 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45910.72069534806</v>
+        <v>45910.72069534722</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Lausanne H</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Lausanne HC – FribourgSuisse - NLA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+56,5%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45910.77071833143</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | EHC Kloten</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EHC Kloten – RapperswilSuisse - NLA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>12/09 17:45</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+56,5%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45910.77071833143</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>92.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>92</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45910.77071833143</v>
+        <v>45910.77071833333</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>12/09 17:45</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>94</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,142 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45910.77071833143</v>
+        <v>45910.77071833333</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liberec – </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Liberec – PardubiceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+99,1%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45910.8036581874</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Litvinov –</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Litvinov – Karlovy VaryRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+93,8%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45910.8036581874</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Vitkovi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HC Vitkovice – HC Rytiri KladnoExtraliga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+67,7%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45910.8036581874</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>150</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45910.8036581874</v>
+        <v>45910.80365818287</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>140</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45910.8036581874</v>
+        <v>45910.80365818287</v>
       </c>
     </row>
     <row r="62">
@@ -3089,23 +3085,66 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>125</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+67,7%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45910.80365818287</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – HC PardubiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>12/09 16:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+67,7%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45910.8036581874</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+73,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45910.849225733</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>12/09 16:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>125</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45910.849225733</v>
+        <v>45910.84922572917</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Vitkovice </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vitkovice – KladnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>12/09 15:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+88,6%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45910.88781627528</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -3171,10 +3171,8 @@
           <t>12/09 15:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>140</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45910.88781627528</v>
+        <v>45910.88781627315</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-10.xlsx
+++ b/data/valuebets_database_2025-09-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3188,6 +3188,51 @@
         <v>45910.88781627315</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Hockey | Pas de buts | IF Brynas </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PMU(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IF Brynas – Växjö LakersHockey européen . Suède - SHL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>13/09 13:15</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+63,6%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45910.97114736919</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
